--- a/data/trans_dic/P36B13_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36B13_R-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 15,99</t>
+          <t>11,13; 16,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,94</t>
+          <t>3,29; 7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,65</t>
+          <t>7,27; 11,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,72</t>
+          <t>2,26; 4,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,03</t>
+          <t>9,69; 13,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,16</t>
+          <t>3,17; 5,51</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,98</t>
+          <t>10,76; 14,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 65,98</t>
+          <t>5,34; 9,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 10,41</t>
+          <t>7,03; 10,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,29</t>
+          <t>2,05; 4,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,02</t>
+          <t>9,18; 11,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 45,2</t>
+          <t>4,03; 6,27</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,88</t>
+          <t>10,71; 15,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,27</t>
+          <t>5,39; 10,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,12</t>
+          <t>5,47; 9,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,43</t>
+          <t>2,52; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,67</t>
+          <t>8,54; 11,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,26</t>
+          <t>4,4; 7,21</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 13,47</t>
+          <t>9,11; 13,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 11,69</t>
+          <t>7,59; 11,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,48</t>
+          <t>5,35; 8,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,0</t>
+          <t>3,88; 6,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,12</t>
+          <t>7,59; 10,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,03</t>
+          <t>5,95; 8,55</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,65</t>
+          <t>11,42; 13,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 35,52</t>
+          <t>6,42; 8,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,81</t>
+          <t>7,01; 8,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,13</t>
+          <t>3,25; 4,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,86</t>
+          <t>9,39; 10,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 19,71</t>
+          <t>5,02; 6,34</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>34692</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51124</t>
+          <t>59299</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72724; 107302</t>
+          <t>74649; 109651</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18326; 43949</t>
+          <t>22632; 52136</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49123; 77549</t>
+          <t>48370; 76838</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15456; 31738</t>
+          <t>16510; 35374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>130358; 174206</t>
+          <t>129463; 175992</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38491; 67449</t>
+          <t>44907; 78166</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311371</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>340695</t>
+          <t>107122</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>107135; 152473</t>
+          <t>109559; 150644</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76717; 786494</t>
+          <t>55999; 97997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71012; 108408</t>
+          <t>73193; 107614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21872; 41063</t>
+          <t>21954; 44825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>190345; 247507</t>
+          <t>188976; 245969</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99914; 971087</t>
+          <t>85350; 132654</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76312</t>
+          <t>90230</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82876; 120198</t>
+          <t>81072; 119148</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36958; 72342</t>
+          <t>43269; 80940</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42360; 71345</t>
+          <t>42801; 71502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12187; 41342</t>
+          <t>20423; 45570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>129707; 179616</t>
+          <t>131382; 179857</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47680; 102470</t>
+          <t>71014; 116494</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>85835</t>
+          <t>94258</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>135449</t>
+          <t>151503</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83720; 125061</t>
+          <t>84571; 122021</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68080; 108231</t>
+          <t>75037; 118202</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55059; 87462</t>
+          <t>55183; 87792</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35138; 65429</t>
+          <t>43199; 74370</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>148918; 198235</t>
+          <t>148657; 200833</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108820; 161847</t>
+          <t>125075; 179864</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>603580</t>
+          <t>408153</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>383818; 460533</t>
+          <t>385296; 460979</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>240232; 1227438</t>
+          <t>226688; 307138</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>247534; 310290</t>
+          <t>246674; 307483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100023; 150946</t>
+          <t>121123; 169961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>651834; 748461</t>
+          <t>647309; 745995</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>356457; 1400988</t>
+          <t>364422; 459804</t>
         </is>
       </c>
     </row>
